--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/41.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/41.xlsx
@@ -426,13 +426,13 @@
         <v>-7.32123205737362</v>
       </c>
       <c r="E2">
-        <v>-19.07522521210733</v>
+        <v>-25.83445721527416</v>
       </c>
       <c r="F2">
-        <v>-4.452836933849873</v>
+        <v>-4.463903093983872</v>
       </c>
       <c r="G2">
-        <v>-13.73242378866329</v>
+        <v>-16.9678480838301</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-7.064101619916367</v>
       </c>
       <c r="E3">
-        <v>-19.52738881329921</v>
+        <v>-25.82604783904192</v>
       </c>
       <c r="F3">
-        <v>-4.276641530539614</v>
+        <v>-4.548818208077447</v>
       </c>
       <c r="G3">
-        <v>-13.08510454300574</v>
+        <v>-16.49386072624495</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-6.851672233361525</v>
       </c>
       <c r="E4">
-        <v>-19.69454837434435</v>
+        <v>-26.18197231062279</v>
       </c>
       <c r="F4">
-        <v>-4.685917983445182</v>
+        <v>-4.55721951027664</v>
       </c>
       <c r="G4">
-        <v>-12.98266302183854</v>
+        <v>-16.13759967858182</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-6.703961798124138</v>
       </c>
       <c r="E5">
-        <v>-20.8110617548315</v>
+        <v>-26.73509823981567</v>
       </c>
       <c r="F5">
-        <v>-4.538975546597383</v>
+        <v>-4.525708414274146</v>
       </c>
       <c r="G5">
-        <v>-12.3760485888591</v>
+        <v>-15.86434559449761</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-6.599602397155508</v>
       </c>
       <c r="E6">
-        <v>-20.51200585983896</v>
+        <v>-26.44138594415218</v>
       </c>
       <c r="F6">
-        <v>-4.351318851901989</v>
+        <v>-4.302428607788762</v>
       </c>
       <c r="G6">
-        <v>-11.98386481154934</v>
+        <v>-15.99789962264288</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-6.536056375932251</v>
       </c>
       <c r="E7">
-        <v>-21.17252455012375</v>
+        <v>-27.25469987592978</v>
       </c>
       <c r="F7">
-        <v>-4.351869716224851</v>
+        <v>-4.377917729205881</v>
       </c>
       <c r="G7">
-        <v>-12.38722499059968</v>
+        <v>-15.7069705359245</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-6.502058809836903</v>
       </c>
       <c r="E8">
-        <v>-20.70593323074344</v>
+        <v>-27.70746576416468</v>
       </c>
       <c r="F8">
-        <v>-3.999029934472012</v>
+        <v>-4.533438738877071</v>
       </c>
       <c r="G8">
-        <v>-12.92055056643073</v>
+        <v>-15.69007020094652</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-6.479884178882741</v>
       </c>
       <c r="E9">
-        <v>-22.33576272542205</v>
+        <v>-28.06270190769638</v>
       </c>
       <c r="F9">
-        <v>-4.162917454911478</v>
+        <v>-4.28948536712002</v>
       </c>
       <c r="G9">
-        <v>-12.5090563769904</v>
+        <v>-15.25687869604181</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-6.456267981827343</v>
       </c>
       <c r="E10">
-        <v>-21.3916438219329</v>
+        <v>-28.66435949282947</v>
       </c>
       <c r="F10">
-        <v>-4.45838699544863</v>
+        <v>-4.243260809309001</v>
       </c>
       <c r="G10">
-        <v>-10.89208992978971</v>
+        <v>-14.65691514905077</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-6.428064873820676</v>
       </c>
       <c r="E11">
-        <v>-23.57863864461924</v>
+        <v>-29.1394009447081</v>
       </c>
       <c r="F11">
-        <v>-4.490454754345805</v>
+        <v>-4.288975092799896</v>
       </c>
       <c r="G11">
-        <v>-12.40828337077498</v>
+        <v>-14.17671058694287</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-6.38482866493476</v>
       </c>
       <c r="E12">
-        <v>-23.84237697082596</v>
+        <v>-29.51571939898251</v>
       </c>
       <c r="F12">
-        <v>-3.38751503547957</v>
+        <v>-4.309570791535699</v>
       </c>
       <c r="G12">
-        <v>-11.57064251733751</v>
+        <v>-13.86188763779479</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-6.316386520206974</v>
       </c>
       <c r="E13">
-        <v>-24.52434704248509</v>
+        <v>-30.70347020408433</v>
       </c>
       <c r="F13">
-        <v>-3.680265045833332</v>
+        <v>-4.295533277527859</v>
       </c>
       <c r="G13">
-        <v>-10.60936271964487</v>
+        <v>-13.86660847573379</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-6.23038659150964</v>
       </c>
       <c r="E14">
-        <v>-25.21825870010244</v>
+        <v>-30.37774838989762</v>
       </c>
       <c r="F14">
-        <v>-3.921309191271751</v>
+        <v>-4.117763147784877</v>
       </c>
       <c r="G14">
-        <v>-11.5538911569088</v>
+        <v>-13.46599936002659</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-6.12892441878791</v>
       </c>
       <c r="E15">
-        <v>-25.72931057729006</v>
+        <v>-31.19209707798597</v>
       </c>
       <c r="F15">
-        <v>-3.871747141194854</v>
+        <v>-3.953114357702238</v>
       </c>
       <c r="G15">
-        <v>-10.78201098006341</v>
+        <v>-13.42411102731819</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-6.012003272376738</v>
       </c>
       <c r="E16">
-        <v>-25.59138684443845</v>
+        <v>-31.93537589499794</v>
       </c>
       <c r="F16">
-        <v>-3.386515196024391</v>
+        <v>-4.155023113562798</v>
       </c>
       <c r="G16">
-        <v>-10.27303777721924</v>
+        <v>-12.75814182336516</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-5.896707869547072</v>
       </c>
       <c r="E17">
-        <v>-26.99371939039373</v>
+        <v>-32.32994183528626</v>
       </c>
       <c r="F17">
-        <v>-3.528256313950011</v>
+        <v>-3.837588582973014</v>
       </c>
       <c r="G17">
-        <v>-9.282999270426952</v>
+        <v>-12.34682309283841</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-5.795495380770845</v>
       </c>
       <c r="E18">
-        <v>-26.43359696885899</v>
+        <v>-32.75208844651829</v>
       </c>
       <c r="F18">
-        <v>-2.7744535745461</v>
+        <v>-3.925336713584163</v>
       </c>
       <c r="G18">
-        <v>-9.293596326698159</v>
+        <v>-12.32362941079028</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-5.710581257442709</v>
       </c>
       <c r="E19">
-        <v>-26.20076094928061</v>
+        <v>-33.41388643071025</v>
       </c>
       <c r="F19">
-        <v>-3.302898962018406</v>
+        <v>-3.689395311346988</v>
       </c>
       <c r="G19">
-        <v>-9.105616929887262</v>
+        <v>-12.33186273754645</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-5.650755388153524</v>
       </c>
       <c r="E20">
-        <v>-28.79597958986241</v>
+        <v>-33.8090637149896</v>
       </c>
       <c r="F20">
-        <v>-2.558291929152972</v>
+        <v>-3.581543532237298</v>
       </c>
       <c r="G20">
-        <v>-8.745836772315888</v>
+        <v>-11.75386466020847</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-5.618598585473833</v>
       </c>
       <c r="E21">
-        <v>-29.59764402225527</v>
+        <v>-34.39776533598675</v>
       </c>
       <c r="F21">
-        <v>-2.596830065833414</v>
+        <v>-3.334493723128582</v>
       </c>
       <c r="G21">
-        <v>-8.224455644790529</v>
+        <v>-11.75091165358744</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-5.604327579953227</v>
       </c>
       <c r="E22">
-        <v>-29.51196076555614</v>
+        <v>-35.30005246083005</v>
       </c>
       <c r="F22">
-        <v>-2.447187151252488</v>
+        <v>-3.333821917164911</v>
       </c>
       <c r="G22">
-        <v>-8.135703229428207</v>
+        <v>-11.7696559624308</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-5.59834516147102</v>
       </c>
       <c r="E23">
-        <v>-28.76199339243484</v>
+        <v>-34.83063084519494</v>
       </c>
       <c r="F23">
-        <v>-2.327135177034367</v>
+        <v>-3.036645939777991</v>
       </c>
       <c r="G23">
-        <v>-7.964706931233772</v>
+        <v>-11.7757506767686</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-5.595805401792077</v>
       </c>
       <c r="E24">
-        <v>-31.21656668728641</v>
+        <v>-35.38962567670177</v>
       </c>
       <c r="F24">
-        <v>-2.450319208402473</v>
+        <v>-3.055458991862971</v>
       </c>
       <c r="G24">
-        <v>-8.924046749240395</v>
+        <v>-11.69959819772874</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-5.584474219005717</v>
       </c>
       <c r="E25">
-        <v>-31.31805658250932</v>
+        <v>-35.57107483747811</v>
       </c>
       <c r="F25">
-        <v>-2.241934276186827</v>
+        <v>-3.088189444682385</v>
       </c>
       <c r="G25">
-        <v>-7.835383780287683</v>
+        <v>-11.33766949610238</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-5.55066395955518</v>
       </c>
       <c r="E26">
-        <v>-29.91978381350192</v>
+        <v>-36.38185282381141</v>
       </c>
       <c r="F26">
-        <v>-2.104626580600989</v>
+        <v>-3.010585501285919</v>
       </c>
       <c r="G26">
-        <v>-8.93902034671452</v>
+        <v>-11.96908322571649</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-5.495082069339632</v>
       </c>
       <c r="E27">
-        <v>-30.40889749835938</v>
+        <v>-35.35145969776512</v>
       </c>
       <c r="F27">
-        <v>-1.916447186074428</v>
+        <v>-2.840369253889065</v>
       </c>
       <c r="G27">
-        <v>-8.207356677080194</v>
+        <v>-11.9828418529777</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-5.413712141927054</v>
       </c>
       <c r="E28">
-        <v>-32.33750891535307</v>
+        <v>-36.45677869050532</v>
       </c>
       <c r="F28">
-        <v>-1.915872299096886</v>
+        <v>-3.075961913449662</v>
       </c>
       <c r="G28">
-        <v>-7.876401439519253</v>
+        <v>-11.80235753126772</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-5.300724944211238</v>
       </c>
       <c r="E29">
-        <v>-31.09030377500455</v>
+        <v>-35.83334593810634</v>
       </c>
       <c r="F29">
-        <v>-1.884497883715854</v>
+        <v>-3.032033590079204</v>
       </c>
       <c r="G29">
-        <v>-7.577770368603757</v>
+        <v>-12.1679046591685</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-5.163037340969873</v>
       </c>
       <c r="E30">
-        <v>-30.44202554996249</v>
+        <v>-35.623555322753</v>
       </c>
       <c r="F30">
-        <v>-1.98760808781192</v>
+        <v>-2.824213604432267</v>
       </c>
       <c r="G30">
-        <v>-8.421880028024967</v>
+        <v>-11.877745274288</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-5.004942381353879</v>
       </c>
       <c r="E31">
-        <v>-30.62066479261707</v>
+        <v>-35.57658146187143</v>
       </c>
       <c r="F31">
-        <v>-1.823506848582532</v>
+        <v>-2.856724539889939</v>
       </c>
       <c r="G31">
-        <v>-9.580918574051505</v>
+        <v>-11.82663376170719</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-4.82588821988916</v>
       </c>
       <c r="E32">
-        <v>-30.10055823165111</v>
+        <v>-35.39206878842891</v>
       </c>
       <c r="F32">
-        <v>-1.403129444112047</v>
+        <v>-2.851352577282784</v>
       </c>
       <c r="G32">
-        <v>-8.801543322105204</v>
+        <v>-12.47022367781475</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-4.632669090970107</v>
       </c>
       <c r="E33">
-        <v>-30.00097708822244</v>
+        <v>-34.41177190609247</v>
       </c>
       <c r="F33">
-        <v>-1.847171648545709</v>
+        <v>-2.915024209331565</v>
       </c>
       <c r="G33">
-        <v>-8.242954973263977</v>
+        <v>-12.43120889863444</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-4.432622924340061</v>
       </c>
       <c r="E34">
-        <v>-30.20421047321268</v>
+        <v>-34.68555891612221</v>
       </c>
       <c r="F34">
-        <v>-1.912891833181613</v>
+        <v>-2.944026180470979</v>
       </c>
       <c r="G34">
-        <v>-7.698820466247208</v>
+        <v>-12.24591435425589</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-4.227352917795956</v>
       </c>
       <c r="E35">
-        <v>-28.65780679094037</v>
+        <v>-34.01308958293118</v>
       </c>
       <c r="F35">
-        <v>-2.067112306030408</v>
+        <v>-2.877338462708605</v>
       </c>
       <c r="G35">
-        <v>-10.044987537201</v>
+        <v>-12.47280259278984</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-4.019434598119754</v>
       </c>
       <c r="E36">
-        <v>-30.63378378181729</v>
+        <v>-33.75691607255428</v>
       </c>
       <c r="F36">
-        <v>-2.265662032072616</v>
+        <v>-2.699164089673056</v>
       </c>
       <c r="G36">
-        <v>-7.696314383273979</v>
+        <v>-12.25629953561258</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-3.816118494311064</v>
       </c>
       <c r="E37">
-        <v>-27.84563856308672</v>
+        <v>-33.57232641505362</v>
       </c>
       <c r="F37">
-        <v>-1.912293751916792</v>
+        <v>-2.844285774969502</v>
       </c>
       <c r="G37">
-        <v>-8.97367513741961</v>
+        <v>-12.47489485757066</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-3.61800942580463</v>
       </c>
       <c r="E38">
-        <v>-28.96922541997385</v>
+        <v>-32.94820307036847</v>
       </c>
       <c r="F38">
-        <v>-1.678313923689446</v>
+        <v>-2.864513678578462</v>
       </c>
       <c r="G38">
-        <v>-8.449000017082676</v>
+        <v>-12.69304325588094</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-3.422466154205594</v>
       </c>
       <c r="E39">
-        <v>-27.34280133774901</v>
+        <v>-32.83464026344112</v>
       </c>
       <c r="F39">
-        <v>-1.922000561142796</v>
+        <v>-2.781486413795868</v>
       </c>
       <c r="G39">
-        <v>-9.002145829057342</v>
+        <v>-12.48210522575519</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-3.234799840128312</v>
       </c>
       <c r="E40">
-        <v>-27.20776677131428</v>
+        <v>-32.2353872980061</v>
       </c>
       <c r="F40">
-        <v>-1.811093763051582</v>
+        <v>-2.72289930086547</v>
       </c>
       <c r="G40">
-        <v>-8.651367044807245</v>
+        <v>-12.36613681551452</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-3.053727897193257</v>
       </c>
       <c r="E41">
-        <v>-26.79198040182602</v>
+        <v>-32.07273356859859</v>
       </c>
       <c r="F41">
-        <v>-2.129071702657602</v>
+        <v>-2.752668340219876</v>
       </c>
       <c r="G41">
-        <v>-8.318478448651371</v>
+        <v>-12.63833318029894</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-2.874004963194461</v>
       </c>
       <c r="E42">
-        <v>-26.27902203708117</v>
+        <v>-32.01103084600708</v>
       </c>
       <c r="F42">
-        <v>-1.43734764478689</v>
+        <v>-2.745081323177636</v>
       </c>
       <c r="G42">
-        <v>-9.072223457032635</v>
+        <v>-12.82501815380398</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-2.696724286282984</v>
       </c>
       <c r="E43">
-        <v>-25.71985512356205</v>
+        <v>-31.67238023852847</v>
       </c>
       <c r="F43">
-        <v>-1.963003919213969</v>
+        <v>-2.641278603932829</v>
       </c>
       <c r="G43">
-        <v>-8.898853497686542</v>
+        <v>-12.6295966506208</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-2.520670999139726</v>
       </c>
       <c r="E44">
-        <v>-25.90965252617153</v>
+        <v>-30.44648383262304</v>
       </c>
       <c r="F44">
-        <v>-1.883229653222168</v>
+        <v>-2.932197922326405</v>
       </c>
       <c r="G44">
-        <v>-9.2826913896918</v>
+        <v>-12.71158562144639</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-2.342490218492134</v>
       </c>
       <c r="E45">
-        <v>-24.20157100064037</v>
+        <v>-30.08430553843758</v>
       </c>
       <c r="F45">
-        <v>-1.882862686462728</v>
+        <v>-2.538295140049392</v>
       </c>
       <c r="G45">
-        <v>-8.502124341351362</v>
+        <v>-12.69629090105496</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-2.163560967737168</v>
       </c>
       <c r="E46">
-        <v>-24.12514394481292</v>
+        <v>-30.16852609803223</v>
       </c>
       <c r="F46">
-        <v>-1.710918464663635</v>
+        <v>-2.62103661807802</v>
       </c>
       <c r="G46">
-        <v>-8.746194311234129</v>
+        <v>-13.12058697009565</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-1.986749033490993</v>
       </c>
       <c r="E47">
-        <v>-22.60364007687178</v>
+        <v>-29.25445588382098</v>
       </c>
       <c r="F47">
-        <v>-2.120032557558254</v>
+        <v>-2.522865140437446</v>
       </c>
       <c r="G47">
-        <v>-8.838965728881126</v>
+        <v>-12.9017665310409</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-1.811964828877876</v>
       </c>
       <c r="E48">
-        <v>-22.9356225063741</v>
+        <v>-29.22836281658878</v>
       </c>
       <c r="F48">
-        <v>-1.667688455013737</v>
+        <v>-2.590172477017114</v>
       </c>
       <c r="G48">
-        <v>-9.108142876133726</v>
+        <v>-13.18806913036816</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-1.639878911924865</v>
       </c>
       <c r="E49">
-        <v>-22.87040342371563</v>
+        <v>-28.75532747869555</v>
       </c>
       <c r="F49">
-        <v>-1.817941048003122</v>
+        <v>-2.567633428354342</v>
       </c>
       <c r="G49">
-        <v>-8.609210557910165</v>
+        <v>-13.26396007631041</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-1.475560688362001</v>
       </c>
       <c r="E50">
-        <v>-22.61403292471939</v>
+        <v>-28.01109088943096</v>
       </c>
       <c r="F50">
-        <v>-2.107605389781456</v>
+        <v>-2.638940122754726</v>
       </c>
       <c r="G50">
-        <v>-9.530098389478153</v>
+        <v>-13.34814393882854</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-1.321546475156105</v>
       </c>
       <c r="E51">
-        <v>-23.26890007944261</v>
+        <v>-27.30718941815269</v>
       </c>
       <c r="F51">
-        <v>-1.602996274324707</v>
+        <v>-2.606332268310926</v>
       </c>
       <c r="G51">
-        <v>-10.42048616499284</v>
+        <v>-13.44474896821001</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-1.180099115338827</v>
       </c>
       <c r="E52">
-        <v>-22.31495438735681</v>
+        <v>-26.96331521590623</v>
       </c>
       <c r="F52">
-        <v>-1.333275706136174</v>
+        <v>-2.496117157001049</v>
       </c>
       <c r="G52">
-        <v>-9.580726562410227</v>
+        <v>-13.56049888244508</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-1.059629080543955</v>
       </c>
       <c r="E53">
-        <v>-20.06640854595821</v>
+        <v>-26.55879568974905</v>
       </c>
       <c r="F53">
-        <v>-1.425797718089656</v>
+        <v>-2.736394234224477</v>
       </c>
       <c r="G53">
-        <v>-9.790658186692031</v>
+        <v>-13.51512785582937</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-0.9663895654486647</v>
       </c>
       <c r="E54">
-        <v>-21.13648242549671</v>
+        <v>-26.19544904926961</v>
       </c>
       <c r="F54">
-        <v>-1.618969682952889</v>
+        <v>-2.515048665624629</v>
       </c>
       <c r="G54">
-        <v>-9.702829413535166</v>
+        <v>-13.37426083258785</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-0.9037333931041172</v>
       </c>
       <c r="E55">
-        <v>-21.4251771719597</v>
+        <v>-25.87390022388097</v>
       </c>
       <c r="F55">
-        <v>-2.147507847574309</v>
+        <v>-2.959591203969581</v>
       </c>
       <c r="G55">
-        <v>-10.01849655179575</v>
+        <v>-13.63783488151523</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-0.8797533321566227</v>
       </c>
       <c r="E56">
-        <v>-19.17312176320515</v>
+        <v>-25.74083101516558</v>
       </c>
       <c r="F56">
-        <v>-1.537840207890109</v>
+        <v>-2.485046855030037</v>
       </c>
       <c r="G56">
-        <v>-9.922940965350231</v>
+        <v>-13.46725074624043</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-0.9000706414460298</v>
       </c>
       <c r="E57">
-        <v>-21.3820842133027</v>
+        <v>-26.11416746930594</v>
       </c>
       <c r="F57">
-        <v>-1.817924480655066</v>
+        <v>-2.894359756101329</v>
       </c>
       <c r="G57">
-        <v>-9.817023371366787</v>
+        <v>-13.42299537347146</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-0.9649563881715399</v>
       </c>
       <c r="E58">
-        <v>-18.86138614099113</v>
+        <v>-25.40587790671423</v>
       </c>
       <c r="F58">
-        <v>-2.09769397380696</v>
+        <v>-2.708269504164628</v>
       </c>
       <c r="G58">
-        <v>-10.25479336075231</v>
+        <v>-13.79077215379294</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-1.076208943720447</v>
       </c>
       <c r="E59">
-        <v>-19.6257427402718</v>
+        <v>-25.33304645924887</v>
       </c>
       <c r="F59">
-        <v>-1.885525887662728</v>
+        <v>-2.722193531838285</v>
       </c>
       <c r="G59">
-        <v>-10.30408076274098</v>
+        <v>-14.20841899211801</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-1.233629779015805</v>
       </c>
       <c r="E60">
-        <v>-18.9721797860628</v>
+        <v>-25.00170254458164</v>
       </c>
       <c r="F60">
-        <v>-1.989832254288437</v>
+        <v>-2.732284703539189</v>
       </c>
       <c r="G60">
-        <v>-10.41338835535664</v>
+        <v>-14.11716049378246</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-1.431323268950209</v>
       </c>
       <c r="E61">
-        <v>-17.75593582250471</v>
+        <v>-25.17300565934379</v>
       </c>
       <c r="F61">
-        <v>-2.087352635150411</v>
+        <v>-2.627151626245487</v>
       </c>
       <c r="G61">
-        <v>-10.43751892179239</v>
+        <v>-14.09528440885895</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-1.661956108350241</v>
       </c>
       <c r="E62">
-        <v>-17.35211368134471</v>
+        <v>-25.1531709431902</v>
       </c>
       <c r="F62">
-        <v>-2.107591307535609</v>
+        <v>-2.795436120859012</v>
       </c>
       <c r="G62">
-        <v>-10.38325245931265</v>
+        <v>-14.6658916932805</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-1.919471940543308</v>
       </c>
       <c r="E63">
-        <v>-19.96140681914235</v>
+        <v>-25.05639745364628</v>
       </c>
       <c r="F63">
-        <v>-2.100622252575857</v>
+        <v>-2.709199760757972</v>
       </c>
       <c r="G63">
-        <v>-9.484886269048326</v>
+        <v>-14.16643630886174</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-2.192925465475207</v>
       </c>
       <c r="E64">
-        <v>-18.50925653062869</v>
+        <v>-24.79715137365517</v>
       </c>
       <c r="F64">
-        <v>-2.279157793799026</v>
+        <v>-2.76961259544414</v>
       </c>
       <c r="G64">
-        <v>-10.55751957649989</v>
+        <v>-14.35002757756033</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-2.468546210282122</v>
       </c>
       <c r="E65">
-        <v>-16.70412075016514</v>
+        <v>-23.988814234812</v>
       </c>
       <c r="F65">
-        <v>-2.214118527168222</v>
+        <v>-2.663085375811526</v>
       </c>
       <c r="G65">
-        <v>-10.818099236987</v>
+        <v>-13.94903112802503</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-2.737227017383316</v>
       </c>
       <c r="E66">
-        <v>-19.04367080522189</v>
+        <v>-23.97910065806555</v>
       </c>
       <c r="F66">
-        <v>-2.15105905863011</v>
+        <v>-2.750379561085941</v>
       </c>
       <c r="G66">
-        <v>-10.93828197169916</v>
+        <v>-14.22234314665618</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-2.988417200983145</v>
       </c>
       <c r="E67">
-        <v>-17.28441752340405</v>
+        <v>-24.4529148934881</v>
       </c>
       <c r="F67">
-        <v>-2.121024113339406</v>
+        <v>-2.915302540778906</v>
       </c>
       <c r="G67">
-        <v>-10.61461324487016</v>
+        <v>-13.93679866225742</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-3.209833222421867</v>
       </c>
       <c r="E68">
-        <v>-18.52948069554695</v>
+        <v>-23.56791068969507</v>
       </c>
       <c r="F68">
-        <v>-1.813536618522437</v>
+        <v>-2.901101010025311</v>
       </c>
       <c r="G68">
-        <v>-10.6264186502632</v>
+        <v>-14.38583443811309</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-3.396107529007976</v>
       </c>
       <c r="E69">
-        <v>-17.49452966041194</v>
+        <v>-24.01925916556557</v>
       </c>
       <c r="F69">
-        <v>-1.768581119572508</v>
+        <v>-2.773976434922088</v>
       </c>
       <c r="G69">
-        <v>-10.24554038597005</v>
+        <v>-14.32834350427811</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-3.542045904862832</v>
       </c>
       <c r="E70">
-        <v>-17.35016643752142</v>
+        <v>-23.83914364038449</v>
       </c>
       <c r="F70">
-        <v>-2.459144634711899</v>
+        <v>-2.930566866910292</v>
       </c>
       <c r="G70">
-        <v>-11.05024793238285</v>
+        <v>-14.08257522453369</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-3.64150289595632</v>
       </c>
       <c r="E71">
-        <v>-16.9251963227456</v>
+        <v>-23.77709448953139</v>
       </c>
       <c r="F71">
-        <v>-2.366531502344109</v>
+        <v>-2.685776844076413</v>
       </c>
       <c r="G71">
-        <v>-10.45820983141283</v>
+        <v>-14.09548966268239</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-3.692200124658307</v>
       </c>
       <c r="E72">
-        <v>-19.20046016078946</v>
+        <v>-24.090949437581</v>
       </c>
       <c r="F72">
-        <v>-2.334496878143046</v>
+        <v>-2.931114417763543</v>
       </c>
       <c r="G72">
-        <v>-9.901965348813407</v>
+        <v>-14.02896093952519</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.693634869129853</v>
       </c>
       <c r="E73">
-        <v>-18.35827720721296</v>
+        <v>-23.72554686990208</v>
       </c>
       <c r="F73">
-        <v>-2.052477539125149</v>
+        <v>-3.231673447623496</v>
       </c>
       <c r="G73">
-        <v>-10.13101868413004</v>
+        <v>-14.22621482966436</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.644393912051623</v>
       </c>
       <c r="E74">
-        <v>-16.99182828929446</v>
+        <v>-24.35083403240719</v>
       </c>
       <c r="F74">
-        <v>-2.197701113612139</v>
+        <v>-3.158082944293593</v>
       </c>
       <c r="G74">
-        <v>-10.54894526355318</v>
+        <v>-13.54734608501756</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.544424062091788</v>
       </c>
       <c r="E75">
-        <v>-18.74200650920093</v>
+        <v>-24.69186435297683</v>
       </c>
       <c r="F75">
-        <v>-2.372833721544608</v>
+        <v>-2.954168710950856</v>
       </c>
       <c r="G75">
-        <v>-10.36689836434865</v>
+        <v>-13.70920362225084</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.398453511903064</v>
       </c>
       <c r="E76">
-        <v>-20.15044343811854</v>
+        <v>-25.04892094305962</v>
       </c>
       <c r="F76">
-        <v>-2.34204330518255</v>
+        <v>-3.129547344001956</v>
       </c>
       <c r="G76">
-        <v>-10.43263255657642</v>
+        <v>-13.63165740353895</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.210260200506401</v>
       </c>
       <c r="E77">
-        <v>-20.54665321447165</v>
+        <v>-24.51583351135067</v>
       </c>
       <c r="F77">
-        <v>-2.987940421595589</v>
+        <v>-3.214035848883089</v>
       </c>
       <c r="G77">
-        <v>-10.60624418574688</v>
+        <v>-13.49238606324735</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-2.983639965471967</v>
       </c>
       <c r="E78">
-        <v>-20.5234810129744</v>
+        <v>-25.64905243245212</v>
       </c>
       <c r="F78">
-        <v>-2.837563573495784</v>
+        <v>-3.128596378223542</v>
       </c>
       <c r="G78">
-        <v>-8.767302349592523</v>
+        <v>-13.41392447869385</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-2.727361794238048</v>
       </c>
       <c r="E79">
-        <v>-20.14709236735287</v>
+        <v>-25.73002607618328</v>
       </c>
       <c r="F79">
-        <v>-2.881351074407765</v>
+        <v>-3.310421366403228</v>
       </c>
       <c r="G79">
-        <v>-10.15932053794527</v>
+        <v>-13.55326534044178</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-2.448129715316006</v>
       </c>
       <c r="E80">
-        <v>-19.96247101053416</v>
+        <v>-26.33717217181367</v>
       </c>
       <c r="F80">
-        <v>-2.983844144788745</v>
+        <v>-3.319566542530135</v>
       </c>
       <c r="G80">
-        <v>-9.175618415315151</v>
+        <v>-13.44295134198218</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.151035481740338</v>
       </c>
       <c r="E81">
-        <v>-21.42322087118838</v>
+        <v>-26.41426038484624</v>
       </c>
       <c r="F81">
-        <v>-2.958106769583765</v>
+        <v>-3.312353119186557</v>
       </c>
       <c r="G81">
-        <v>-9.199259021011088</v>
+        <v>-13.46222202756628</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-1.843975371177272</v>
       </c>
       <c r="E82">
-        <v>-21.65037365588714</v>
+        <v>-27.08754031488464</v>
       </c>
       <c r="F82">
-        <v>-2.549777140619596</v>
+        <v>-3.597432447390395</v>
       </c>
       <c r="G82">
-        <v>-9.048735136431505</v>
+        <v>-12.95431482038576</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-1.534439132277104</v>
       </c>
       <c r="E83">
-        <v>-22.6398995682512</v>
+        <v>-27.70528756816699</v>
       </c>
       <c r="F83">
-        <v>-2.831117218367198</v>
+        <v>-3.740302630086032</v>
       </c>
       <c r="G83">
-        <v>-8.662454061818265</v>
+        <v>-12.68863029867709</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-1.227880954334786</v>
       </c>
       <c r="E84">
-        <v>-23.0290811529444</v>
+        <v>-28.54343565140265</v>
       </c>
       <c r="F84">
-        <v>-3.11384232641228</v>
+        <v>-3.670131627394885</v>
       </c>
       <c r="G84">
-        <v>-9.042587453365078</v>
+        <v>-12.80087765573161</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-0.9308586607558919</v>
       </c>
       <c r="E85">
-        <v>-23.04934607412872</v>
+        <v>-28.52682520874251</v>
       </c>
       <c r="F85">
-        <v>-2.517924757247149</v>
+        <v>-3.590584334071452</v>
       </c>
       <c r="G85">
-        <v>-8.114224409969417</v>
+        <v>-12.4018443597011</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-0.6516228101482902</v>
       </c>
       <c r="E86">
-        <v>-23.79574727396898</v>
+        <v>-30.14834948209106</v>
       </c>
       <c r="F86">
-        <v>-2.64771170518297</v>
+        <v>-3.742024805916452</v>
       </c>
       <c r="G86">
-        <v>-8.221790655631416</v>
+        <v>-12.33681200312766</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-0.3960319787736537</v>
       </c>
       <c r="E87">
-        <v>-26.90510168253763</v>
+        <v>-30.35539131372175</v>
       </c>
       <c r="F87">
-        <v>-3.723171163828735</v>
+        <v>-3.781435213472041</v>
       </c>
       <c r="G87">
-        <v>-6.949008385966597</v>
+        <v>-12.49958490620254</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-0.1707255641407724</v>
       </c>
       <c r="E88">
-        <v>-27.4093925480318</v>
+        <v>-31.27804977888855</v>
       </c>
       <c r="F88">
-        <v>-3.101909693974953</v>
+        <v>-3.732622007527274</v>
       </c>
       <c r="G88">
-        <v>-7.720150311156732</v>
+        <v>-12.38601333093231</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>0.01075256448740645</v>
       </c>
       <c r="E89">
-        <v>-29.41501745823694</v>
+        <v>-32.3236517848896</v>
       </c>
       <c r="F89">
-        <v>-3.1632039115777</v>
+        <v>-3.896534378988824</v>
       </c>
       <c r="G89">
-        <v>-7.707805286840789</v>
+        <v>-12.40486357723292</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>0.1371685784959723</v>
       </c>
       <c r="E90">
-        <v>-29.60679606822477</v>
+        <v>-33.85566397676553</v>
       </c>
       <c r="F90">
-        <v>-3.020908615859606</v>
+        <v>-4.161766852588989</v>
       </c>
       <c r="G90">
-        <v>-7.278020333295986</v>
+        <v>-12.48831249864133</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>0.2001682806935321</v>
       </c>
       <c r="E91">
-        <v>-30.0423424340455</v>
+        <v>-34.08121141742857</v>
       </c>
       <c r="F91">
-        <v>-2.729826937455083</v>
+        <v>-4.318387934171097</v>
       </c>
       <c r="G91">
-        <v>-7.072965142593529</v>
+        <v>-12.28564421127268</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>0.1870180710380602</v>
       </c>
       <c r="E92">
-        <v>-32.64029627292793</v>
+        <v>-35.5579649052259</v>
       </c>
       <c r="F92">
-        <v>-3.37982778598159</v>
+        <v>-4.058225069076065</v>
       </c>
       <c r="G92">
-        <v>-7.673312712867123</v>
+        <v>-12.7487034580327</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>0.08985270072350844</v>
       </c>
       <c r="E93">
-        <v>-33.62911121487279</v>
+        <v>-37.06816570204388</v>
       </c>
       <c r="F93">
-        <v>-3.49828432458192</v>
+        <v>-4.285120699274669</v>
       </c>
       <c r="G93">
-        <v>-8.350676814566322</v>
+        <v>-12.67292507063878</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-0.09119245933950422</v>
       </c>
       <c r="E94">
-        <v>-35.32704895862678</v>
+        <v>-38.92720617285774</v>
       </c>
       <c r="F94">
-        <v>-3.382423061054561</v>
+        <v>-4.159529432234027</v>
       </c>
       <c r="G94">
-        <v>-8.568600095779926</v>
+        <v>-12.49189450891482</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-0.3571534795100286</v>
       </c>
       <c r="E95">
-        <v>-36.57580057284892</v>
+        <v>-40.3333584866385</v>
       </c>
       <c r="F95">
-        <v>-3.397524198807596</v>
+        <v>-4.414539852083647</v>
       </c>
       <c r="G95">
-        <v>-8.418231806840689</v>
+        <v>-13.0896697853044</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-0.7096208814258986</v>
       </c>
       <c r="E96">
-        <v>-37.76619147829721</v>
+        <v>-41.76822811833888</v>
       </c>
       <c r="F96">
-        <v>-3.553639976273996</v>
+        <v>-4.412029898853165</v>
       </c>
       <c r="G96">
-        <v>-7.928578947763707</v>
+        <v>-12.81981397621625</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-1.132160870650767</v>
       </c>
       <c r="E97">
-        <v>-40.18439433415617</v>
+        <v>-43.14167352859923</v>
       </c>
       <c r="F97">
-        <v>-3.404435268049153</v>
+        <v>-4.62527900445805</v>
       </c>
       <c r="G97">
-        <v>-8.120418440673394</v>
+        <v>-13.1258176320477</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-1.628840409072324</v>
       </c>
       <c r="E98">
-        <v>-41.70214862561896</v>
+        <v>-44.7929091199121</v>
       </c>
       <c r="F98">
-        <v>-4.005622910630893</v>
+        <v>-4.780810782905476</v>
       </c>
       <c r="G98">
-        <v>-9.421654849248247</v>
+        <v>-13.26022909148765</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-2.168670862892198</v>
       </c>
       <c r="E99">
-        <v>-43.74568592021631</v>
+        <v>-46.2313245467605</v>
       </c>
       <c r="F99">
-        <v>-3.678267023657779</v>
+        <v>-4.664803726715225</v>
       </c>
       <c r="G99">
-        <v>-7.774552506003575</v>
+        <v>-13.71256879179151</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-2.768495601187225</v>
       </c>
       <c r="E100">
-        <v>-45.20698599046247</v>
+        <v>-48.06496480686533</v>
       </c>
       <c r="F100">
-        <v>-3.638740644665798</v>
+        <v>-4.919548240628546</v>
       </c>
       <c r="G100">
-        <v>-9.338583330031316</v>
+        <v>-13.38506645322803</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-3.361050216014322</v>
       </c>
       <c r="E101">
-        <v>-47.08542191545118</v>
+        <v>-49.63717739462586</v>
       </c>
       <c r="F101">
-        <v>-4.116889220174923</v>
+        <v>-5.244145664150338</v>
       </c>
       <c r="G101">
-        <v>-9.464192048882342</v>
+        <v>-14.06689482558693</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.019045790545801</v>
       </c>
       <c r="E102">
-        <v>-49.91630687186615</v>
+        <v>-52.26845061313823</v>
       </c>
       <c r="F102">
-        <v>-4.072817589243781</v>
+        <v>-5.25904468025709</v>
       </c>
       <c r="G102">
-        <v>-9.128366998833135</v>
+        <v>-14.35046291429875</v>
       </c>
     </row>
   </sheetData>
